--- a/outputs/validation_truss_supp_disp.xlsx
+++ b/outputs/validation_truss_supp_disp.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2.382099995410737e-18</v>
+        <v>1.3799594640821e-18</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009396370204486366</v>
+        <v>0.00939637020448634</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="F5" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007030213617920157</v>
+        <v>0.007030213617920176</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006103848963633275</v>
+        <v>0.006103848963633243</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002301066941486609</v>
+        <v>0.002301066941486712</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01232145663144493</v>
+        <v>0.01232145663144494</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="F10" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="G10" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006769741737365751</v>
+        <v>0.006769741737365922</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.005336394045431754</v>
+        <v>0.005336394045432011</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.009856829270822563</v>
+        <v>0.009856829270822811</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="F13" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.009079071053007792</v>
+        <v>0.009079071053008071</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="F15" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
     </row>
   </sheetData>
@@ -1038,13 +1038,13 @@
         <v>0.01338717641439762</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
     </row>
     <row r="3">
@@ -1057,16 +1057,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
     </row>
     <row r="4">
@@ -1079,16 +1079,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
     </row>
     <row r="5">
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.831690603168681e-13</v>
+        <v>2.700062395888381e-13</v>
       </c>
       <c r="C2" t="n">
-        <v>2.728484105318785e-12</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98656052374835</v>
+        <v>23.98656052374821</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-2.700062395888381e-12</v>
+        <v>-8.242295734817162e-13</v>
       </c>
       <c r="D3" t="n">
-        <v>-23.98656052374853</v>
+        <v>-23.98656052374844</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-23.98656052374873</v>
+        <v>-23.98656052374835</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>23.98656052374851</v>
+        <v>23.98656052374813</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="G2" t="n">
-        <v>9.891890839513024e-05</v>
+        <v>9.891890839513561e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>27.69729435063647</v>
+        <v>27.69729435063797</v>
       </c>
       <c r="I2" t="n">
-        <v>6924.323587659116</v>
+        <v>6924.323587659492</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0006677026316671839</v>
+        <v>-0.0006677026316671804</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001284994313772234</v>
+        <v>-0.0001284994313772227</v>
       </c>
       <c r="H3" t="n">
-        <v>-35.97984078562255</v>
+        <v>-35.97984078562236</v>
       </c>
       <c r="I3" t="n">
-        <v>-8994.960196405636</v>
+        <v>-8994.960196405589</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>2.602085213965211e-18</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.891205793294678e-19</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>2.42861286636753e-13</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>6.071532165918825e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.445602896647339e-19</v>
+        <v>-2.891205793294678e-19</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.04768811061255e-14</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.011922027653137e-11</v>
+        <v>-2.023844055306275e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.938187887435717e-17</v>
+        <v>-4.662069341687669e-18</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.896979812392861e-18</v>
+        <v>-7.770115569479449e-19</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.371154347470001e-12</v>
+        <v>-2.175632359454245e-13</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.427885868675003e-10</v>
+        <v>-5.439080898635613e-11</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.168404344971009e-18</v>
+        <v>-2.602085213965211e-18</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.614007241618348e-19</v>
+        <v>-4.336808689942018e-19</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.011922027653137e-13</v>
+        <v>-1.214306433183765e-13</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.529805069132843e-11</v>
+        <v>-3.035766082959412e-11</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002225675438890678</v>
+        <v>0.0002225675438890656</v>
       </c>
       <c r="G9" t="n">
-        <v>4.283314379240905e-05</v>
+        <v>4.283314379240863e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>11.99328026187453</v>
+        <v>11.99328026187442</v>
       </c>
       <c r="I9" t="n">
-        <v>2998.320065468633</v>
+        <v>2998.320065468604</v>
       </c>
     </row>
     <row r="10">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0005935134503708455</v>
+        <v>-0.000593513450370829</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.891890839514092e-05</v>
+        <v>-9.891890839513817e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>-27.69729435063945</v>
+        <v>-27.69729435063869</v>
       </c>
       <c r="I11" t="n">
-        <v>-6924.323587659863</v>
+        <v>-6924.323587659671</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0006677026316671939</v>
+        <v>0.0006677026316671839</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001284994313772253</v>
+        <v>0.0001284994313772234</v>
       </c>
       <c r="H12" t="n">
-        <v>35.97984078562308</v>
+        <v>35.97984078562255</v>
       </c>
       <c r="I12" t="n">
-        <v>8994.960196405771</v>
+        <v>8994.960196405636</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.891890839513101e-05</v>
+        <v>-9.891890839513655e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>-27.69729435063668</v>
+        <v>-27.69729435063823</v>
       </c>
       <c r="I13" t="n">
-        <v>-6924.323587659171</v>
+        <v>-6924.323587659558</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0006677026316671881</v>
+        <v>0.0006677026316671856</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001284994313772242</v>
+        <v>0.0001284994313772237</v>
       </c>
       <c r="H14" t="n">
-        <v>35.97984078562278</v>
+        <v>35.97984078562264</v>
       </c>
       <c r="I14" t="n">
-        <v>8994.960196405695</v>
+        <v>8994.96019640566</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>6.505213034913027e-19</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.168404344971009e-19</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>6.071532165918825e-14</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.517883041479706e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002225675438890636</v>
+        <v>0.0002225675438890622</v>
       </c>
       <c r="G16" t="n">
-        <v>4.283314379240823e-05</v>
+        <v>4.283314379240796e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>11.99328026187431</v>
+        <v>11.99328026187423</v>
       </c>
       <c r="I16" t="n">
-        <v>2998.320065468577</v>
+        <v>2998.320065468557</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.807003620809174e-20</v>
+        <v>-1.445602896647339e-19</v>
       </c>
       <c r="H17" t="n">
-        <v>-5.059610138265687e-15</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.264902534566422e-12</v>
+        <v>-1.011922027653137e-11</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>2.482822974991805e-17</v>
+        <v>-6.505213034913027e-19</v>
       </c>
       <c r="G18" t="n">
-        <v>4.138038291653008e-18</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="H18" t="n">
-        <v>1.158650721662842e-12</v>
+        <v>-3.035766082959412e-14</v>
       </c>
       <c r="I18" t="n">
-        <v>2.896626804157106e-10</v>
+        <v>-7.589415207398531e-12</v>
       </c>
     </row>
     <row r="19">
@@ -1802,16 +1802,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.192622389734055e-18</v>
+        <v>-7.589415207398531e-19</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.987703982890091e-19</v>
+        <v>-1.264902534566422e-19</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.565571152092256e-14</v>
+        <v>-3.541727096785981e-14</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.391392788023064e-11</v>
+        <v>-8.854317741964952e-12</v>
       </c>
     </row>
     <row r="20">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0002225675438890618</v>
+        <v>-0.0002225675438890598</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.28331437924079e-05</v>
+        <v>-4.28331437924075e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.99328026187421</v>
+        <v>-11.9932802618741</v>
       </c>
       <c r="I20" t="n">
-        <v>-2998.320065468553</v>
+        <v>-2998.320065468525</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>8.673617379884035e-19</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2.891205793294678e-19</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0005935134503708407</v>
+        <v>0.0005935134503708229</v>
       </c>
       <c r="G22" t="n">
-        <v>9.891890839514012e-05</v>
+        <v>9.891890839513715e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>27.69729435063923</v>
+        <v>27.6972943506384</v>
       </c>
       <c r="I22" t="n">
-        <v>6924.323587659808</v>
+        <v>6924.3235876596</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0006677026316671884</v>
+        <v>-0.0006677026316671785</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0001284994313772243</v>
+        <v>-0.0001284994313772223</v>
       </c>
       <c r="H23" t="n">
-        <v>-35.97984078562279</v>
+        <v>-35.97984078562226</v>
       </c>
       <c r="I23" t="n">
-        <v>-8994.960196405698</v>
+        <v>-8994.960196405564</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.94033331803579e-19</v>
+        <v>-4.599864880273667e-19</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.223293329050021e-13</v>
+        <v>-1.287962166476626e-13</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.558233322625052e-11</v>
+        <v>-3.219905416191566e-11</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-2.891205793294678e-19</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-2.023844055306275e-11</v>
       </c>
     </row>
     <row r="26">
@@ -2019,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>8.673617379884035e-19</v>
+        <v>1.301042606982605e-18</v>
       </c>
       <c r="G26" t="n">
-        <v>2.891205793294678e-19</v>
+        <v>4.336808689942018e-19</v>
       </c>
       <c r="H26" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>1.214306433183765e-13</v>
       </c>
       <c r="I26" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>3.035766082959412e-11</v>
       </c>
     </row>
     <row r="27">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.734723475976807e-18</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.782411586589357e-19</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.61907524424502e-13</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-4.04768811061255e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.000296756725185413</v>
+        <v>-0.0002967567251854122</v>
       </c>
       <c r="G31" t="n">
-        <v>-4.945945419756884e-05</v>
+        <v>-4.94594541975687e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-13.84864717531928</v>
+        <v>-13.84864717531923</v>
       </c>
       <c r="I31" t="n">
-        <v>-3462.161793829819</v>
+        <v>-3462.161793829809</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0002967567251854168</v>
+        <v>0.0002967567251854162</v>
       </c>
       <c r="G32" t="n">
-        <v>4.945945419756947e-05</v>
+        <v>4.945945419756938e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>13.84864717531945</v>
+        <v>13.84864717531942</v>
       </c>
       <c r="I32" t="n">
-        <v>3462.161793829863</v>
+        <v>3462.161793829856</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003709459064817539</v>
+        <v>0.0003709459064817586</v>
       </c>
       <c r="G33" t="n">
-        <v>5.529735085789877e-05</v>
+        <v>5.529735085789947e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>15.48325824021166</v>
+        <v>15.48325824021185</v>
       </c>
       <c r="I33" t="n">
-        <v>3870.814560052914</v>
+        <v>3870.814560052963</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0003709459064817588</v>
+        <v>-0.0003709459064817636</v>
       </c>
       <c r="G34" t="n">
-        <v>-5.52973508578995e-05</v>
+        <v>-5.529735085790022e-05</v>
       </c>
       <c r="H34" t="n">
-        <v>-15.48325824021186</v>
+        <v>-15.48325824021206</v>
       </c>
       <c r="I34" t="n">
-        <v>-3870.814560052966</v>
+        <v>-3870.814560053016</v>
       </c>
     </row>
     <row r="35">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0002967567251854178</v>
+        <v>0.0002967567251854169</v>
       </c>
       <c r="G36" t="n">
-        <v>4.945945419756963e-05</v>
+        <v>4.945945419756949e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>13.8486471753195</v>
+        <v>13.84864717531946</v>
       </c>
       <c r="I36" t="n">
-        <v>3462.161793829874</v>
+        <v>3462.161793829864</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0003709459064817559</v>
+        <v>0.0003709459064817604</v>
       </c>
       <c r="G37" t="n">
-        <v>5.529735085789907e-05</v>
+        <v>5.529735085789974e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>15.48325824021174</v>
+        <v>15.48325824021193</v>
       </c>
       <c r="I37" t="n">
-        <v>3870.814560052935</v>
+        <v>3870.814560052982</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0003709459064817596</v>
+        <v>-0.0003709459064817648</v>
       </c>
       <c r="G38" t="n">
-        <v>-5.529735085789961e-05</v>
+        <v>-5.529735085790039e-05</v>
       </c>
       <c r="H38" t="n">
-        <v>-15.48325824021189</v>
+        <v>-15.48325824021211</v>
       </c>
       <c r="I38" t="n">
-        <v>-3870.814560052973</v>
+        <v>-3870.814560053027</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0002967567251854148</v>
+        <v>-0.0002967567251854104</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.945945419756913e-05</v>
+        <v>-4.945945419756841e-05</v>
       </c>
       <c r="H39" t="n">
-        <v>-13.84864717531936</v>
+        <v>-13.84864717531915</v>
       </c>
       <c r="I39" t="n">
-        <v>-3462.161793829839</v>
+        <v>-3462.161793829788</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0002967567251854191</v>
+        <v>0.0002967567251854139</v>
       </c>
       <c r="G40" t="n">
-        <v>4.945945419756985e-05</v>
+        <v>4.945945419756898e-05</v>
       </c>
       <c r="H40" t="n">
-        <v>13.84864717531956</v>
+        <v>13.84864717531931</v>
       </c>
       <c r="I40" t="n">
-        <v>3462.16179382989</v>
+        <v>3462.161793829829</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00037094590648176</v>
+        <v>0.0003709459064817643</v>
       </c>
       <c r="G41" t="n">
-        <v>5.529735085789968e-05</v>
+        <v>5.529735085790033e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>15.48325824021191</v>
+        <v>15.48325824021209</v>
       </c>
       <c r="I41" t="n">
-        <v>3870.814560052978</v>
+        <v>3870.814560053023</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.0003709459064817648</v>
+        <v>-0.0003709459064817696</v>
       </c>
       <c r="G42" t="n">
-        <v>-5.529735085790039e-05</v>
+        <v>-5.529735085790111e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>-15.48325824021211</v>
+        <v>-15.48325824021231</v>
       </c>
       <c r="I42" t="n">
-        <v>-3870.814560053027</v>
+        <v>-3870.814560053077</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.0002967567251854161</v>
+        <v>-0.0002967567251854109</v>
       </c>
       <c r="G43" t="n">
-        <v>-4.945945419756935e-05</v>
+        <v>-4.945945419756848e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>-13.84864717531942</v>
+        <v>-13.84864717531917</v>
       </c>
       <c r="I43" t="n">
-        <v>-3462.161793829854</v>
+        <v>-3462.161793829794</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0002967567251854191</v>
+        <v>0.0002967567251854143</v>
       </c>
       <c r="G44" t="n">
-        <v>4.945945419756985e-05</v>
+        <v>4.945945419756906e-05</v>
       </c>
       <c r="H44" t="n">
-        <v>13.84864717531956</v>
+        <v>13.84864717531934</v>
       </c>
       <c r="I44" t="n">
-        <v>3462.16179382989</v>
+        <v>3462.161793829834</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>27.69729435063647</v>
+        <v>27.69729435063797</v>
       </c>
       <c r="F2" t="n">
-        <v>6924.323587659116</v>
+        <v>6924.323587659492</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.002016487163610053</v>
+        <v>-0.002016487163610129</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-27.69729435063647</v>
+        <v>-27.69729435063797</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>27.69729435063647</v>
+        <v>27.69729435063797</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>-35.97984078562255</v>
+        <v>-35.97984078562236</v>
       </c>
       <c r="F3" t="n">
-        <v>-8994.960196405636</v>
+        <v>-8994.960196405589</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.004332297368332816</v>
+        <v>0.00433229736833282</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.004665991516016643</v>
+        <v>-0.004665991516016574</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.006910245705078541</v>
+        <v>-0.006910245705078549</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>35.97984078562254</v>
+        <v>35.97984078562237</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-35.97984078562254</v>
+        <v>-35.97984078562237</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>2.42861286636753e-13</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>6.071532165918825e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.004665991516016644</v>
+        <v>-0.004665991516016575</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004332297368332817</v>
+        <v>0.00433229736833282</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.004665991516016645</v>
+        <v>-0.004665991516016573</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003379241758487188</v>
+        <v>0.003379241758487184</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3219,13 +3219,13 @@
         <v>-2998.320065468499</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.004332297368332816</v>
+        <v>0.00433229736833282</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.004665991516016643</v>
+        <v>-0.004665991516016574</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.006910245705078541</v>
+        <v>-0.006910245705078549</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004109729824443758</v>
+        <v>0.004109729824443762</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003400749071457136</v>
+        <v>-0.003400749071457051</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.0122784982336304</v>
+        <v>-0.01227849823363042</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>11.99328026187402</v>
+        <v>11.99328026187399</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-11.99328026187402</v>
+        <v>-11.99328026187399</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.04768811061255e-14</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.011922027653137e-11</v>
+        <v>-2.023844055306275e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.005259504966387426</v>
+        <v>0.005259504966387387</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.002351246307469485</v>
+        <v>-0.002351246307469425</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.002016487163610053</v>
+        <v>-0.002016487163610129</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.005259504966387425</v>
+        <v>0.005259504966387385</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0008902701755563423</v>
+        <v>-0.0008902701755562667</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0122784982336304</v>
+        <v>-0.01227849823363042</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.371154347470001e-12</v>
+        <v>-2.175632359454245e-13</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.427885868675003e-10</v>
+        <v>-5.439080898635613e-11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="O7" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.002016487163610053</v>
+        <v>-0.002016487163610129</v>
       </c>
       <c r="U7" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.005220001227961625</v>
+        <v>-0.005220001227961893</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.371347480016993e-12</v>
+        <v>2.167155344068306e-13</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.371347480016993e-12</v>
+        <v>-2.167155344068306e-13</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.011922027653137e-13</v>
+        <v>-1.214306433183765e-13</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.529805069132843e-11</v>
+        <v>-3.035766082959412e-11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="N8" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="O8" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.003400749071457137</v>
+        <v>-0.003400749071457052</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004109729824443758</v>
+        <v>0.004109729824443762</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.003400749071457139</v>
+        <v>-0.003400749071457054</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002648753692530583</v>
+        <v>0.0026487536925306</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>11.99328026187453</v>
+        <v>11.99328026187442</v>
       </c>
       <c r="F9" t="n">
-        <v>2998.320065468633</v>
+        <v>2998.320065468604</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0008902701755563425</v>
+        <v>-0.0008902701755562669</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005259504966387424</v>
+        <v>0.005259504966387384</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0006677026316672747</v>
+        <v>-0.0006677026316672012</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003994262521827891</v>
+        <v>0.003994262521827863</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-11.99328026187453</v>
+        <v>-11.99328026187442</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>11.99328026187453</v>
+        <v>11.99328026187442</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3859,13 +3859,13 @@
         <v>2.023844055306275e-11</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="O10" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.003994262521827891</v>
+        <v>0.003994262521827863</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.001620758241512932</v>
+        <v>-0.00162075824151285</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.005220001227961625</v>
+        <v>-0.005220001227961893</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003994262521827892</v>
+        <v>0.003994262521827864</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.0006677026316672745</v>
+        <v>-0.000667702631667201</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.008986496724337585</v>
+        <v>-0.008986496724337876</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>-27.69729435063945</v>
+        <v>-27.69729435063869</v>
       </c>
       <c r="F11" t="n">
-        <v>-6924.323587659863</v>
+        <v>-6924.323587659671</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N11" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.005220001227961625</v>
+        <v>-0.005220001227961893</v>
       </c>
       <c r="U11" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.007236488391571465</v>
+        <v>-0.00723648839157201</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>27.69729435063946</v>
+        <v>27.69729435063869</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-27.69729435063946</v>
+        <v>-27.69729435063869</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>35.97984078562308</v>
+        <v>35.97984078562255</v>
       </c>
       <c r="F12" t="n">
-        <v>8994.960196405771</v>
+        <v>8994.960196405636</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="I12" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0006677026316672747</v>
+        <v>-0.0006677026316672012</v>
       </c>
       <c r="T12" t="n">
-        <v>0.003994262521827891</v>
+        <v>0.003994262521827863</v>
       </c>
       <c r="U12" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-8.089388844182754e-17</v>
+        <v>-1.734139969346397e-17</v>
       </c>
       <c r="Z12" t="n">
-        <v>-4.670410826768469e-17</v>
+        <v>-1.001206178114632e-17</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-35.97984078562309</v>
+        <v>-35.97984078562254</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>35.97984078562309</v>
+        <v>35.97984078562254</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>-27.69729435063668</v>
+        <v>-27.69729435063823</v>
       </c>
       <c r="F13" t="n">
-        <v>-6924.323587659171</v>
+        <v>-6924.323587659558</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.382099995410737e-18</v>
+        <v>1.3799594640821e-18</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.002016487163610054</v>
+        <v>-0.002016487163610131</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>27.69729435063669</v>
+        <v>27.69729435063824</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-27.69729435063669</v>
+        <v>-27.69729435063824</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>35.97984078562278</v>
+        <v>35.97984078562264</v>
       </c>
       <c r="F14" t="n">
-        <v>8994.960196405695</v>
+        <v>8994.96019640566</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="N14" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.382099995410737e-18</v>
+        <v>1.3799594640821e-18</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0006677026316671881</v>
+        <v>0.0006677026316671856</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.001107511175879645</v>
+        <v>-0.001107511175879719</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.006910245705078541</v>
+        <v>-0.006910245705078548</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-35.97984078562278</v>
+        <v>-35.97984078562264</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>35.97984078562278</v>
+        <v>35.97984078562264</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>6.071532165918825e-14</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.517883041479706e-11</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="H15" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.001107511175879645</v>
+        <v>-0.001107511175879719</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0006677026316671881</v>
+        <v>0.0006677026316671856</v>
       </c>
       <c r="U15" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.001107511175879644</v>
+        <v>-0.001107511175879719</v>
       </c>
       <c r="Z15" t="n">
-        <v>-4.590842515384225e-05</v>
+        <v>-4.590842515383748e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>11.99328026187431</v>
+        <v>11.99328026187423</v>
       </c>
       <c r="F16" t="n">
-        <v>2998.320065468577</v>
+        <v>2998.320065468557</v>
       </c>
       <c r="G16" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="H16" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0006677026316671881</v>
+        <v>0.0006677026316671856</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.001107511175879645</v>
+        <v>-0.001107511175879719</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.006910245705078541</v>
+        <v>-0.006910245705078548</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0008902701755562517</v>
+        <v>0.0008902701755562478</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.0005139977255089752</v>
+        <v>0.000513997725508887</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.0122784982336304</v>
+        <v>-0.01227849823363042</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-11.9932802618743</v>
+        <v>-11.99328026187423</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>11.9932802618743</v>
+        <v>11.99328026187423</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.059610138265687e-15</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.264902534566422e-12</v>
+        <v>-1.011922027653137e-11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="N17" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0005139977255088585</v>
+        <v>0.0005139977255089</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0009820870258638687</v>
+        <v>-0.0009820870258639312</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.002016487163610054</v>
+        <v>-0.002016487163610131</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0005139977255088584</v>
+        <v>0.0005139977255088991</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.0008902701755563192</v>
+        <v>0.000890270175556241</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.0122784982336304</v>
+        <v>-0.01227849823363042</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>3.907985046680551e-14</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>-3.907985046680551e-14</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>1.158650721662842e-12</v>
+        <v>-3.035766082959412e-14</v>
       </c>
       <c r="F18" t="n">
-        <v>2.896626804157106e-10</v>
+        <v>-7.589415207398531e-12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.002016487163610054</v>
+        <v>-0.002016487163610131</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.005220001227961625</v>
+        <v>-0.005220001227961893</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-1.158184659288963e-12</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.158184659288963e-12</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.565571152092256e-14</v>
+        <v>-3.541727096785981e-14</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.391392788023064e-11</v>
+        <v>-8.854317741964952e-12</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="I19" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0005139977255089752</v>
+        <v>0.000513997725508887</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0008902701755562518</v>
+        <v>0.0008902701755562479</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0005139977255089741</v>
+        <v>0.0005139977255088862</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0009820870258639069</v>
+        <v>-0.0009820870258639238</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>3.552713678800501e-14</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-3.552713678800501e-14</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>-11.99328026187421</v>
+        <v>-11.9932802618741</v>
       </c>
       <c r="F20" t="n">
-        <v>-2998.320065468553</v>
+        <v>-2998.320065468525</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="I20" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="N20" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0008902701755563191</v>
+        <v>0.0008902701755562408</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0005139977255088584</v>
+        <v>0.0005139977255088991</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0006677026316672573</v>
+        <v>0.0006677026316671811</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.001107511175879734</v>
+        <v>-0.001107511175879706</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>11.99328026187421</v>
+        <v>11.99328026187411</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>-11.99328026187421</v>
+        <v>-11.99328026187411</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="N21" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.001107511175879735</v>
+        <v>-0.001107511175879706</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.590842515376115e-05</v>
+        <v>-4.590842515384577e-05</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.005220001227961625</v>
+        <v>-0.005220001227961893</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.001107511175879734</v>
+        <v>-0.001107511175879706</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.0006677026316672573</v>
+        <v>0.0006677026316671811</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.008986496724337583</v>
+        <v>-0.008986496724337874</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>27.69729435063923</v>
+        <v>27.6972943506384</v>
       </c>
       <c r="F22" t="n">
-        <v>6924.323587659808</v>
+        <v>6924.3235876596</v>
       </c>
       <c r="G22" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N22" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.005220001227961625</v>
+        <v>-0.005220001227961893</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.007236488391571465</v>
+        <v>-0.00723648839157201</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-27.69729435063924</v>
+        <v>-27.69729435063841</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>27.69729435063924</v>
+        <v>27.69729435063841</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>-35.97984078562279</v>
+        <v>-35.97984078562226</v>
       </c>
       <c r="F23" t="n">
-        <v>-8994.960196405698</v>
+        <v>-8994.960196405564</v>
       </c>
       <c r="G23" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="H23" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N23" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0006677026316672573</v>
+        <v>0.0006677026316671811</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.001107511175879734</v>
+        <v>-0.001107511175879706</v>
       </c>
       <c r="U23" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>6.883107581431855e-17</v>
+        <v>2.552293411161106e-18</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.973964015000836e-17</v>
+        <v>1.473567287984773e-18</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>35.97984078562279</v>
+        <v>35.97984078562226</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>-35.97984078562279</v>
+        <v>-35.97984078562226</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.223293329050021e-13</v>
+        <v>-1.287962166476626e-13</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.558233322625052e-11</v>
+        <v>-3.219905416191566e-11</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.223293329050021e-13</v>
+        <v>1.287962166476627e-13</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>-2.223293329050021e-13</v>
+        <v>-1.287962166476627e-13</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-2.023844055306275e-11</v>
       </c>
       <c r="G25" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="H25" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="I25" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="N25" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="T25" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="U25" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5901,19 +5901,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>8.095376221225099e-14</v>
+        <v>1.214306433183765e-13</v>
       </c>
       <c r="F26" t="n">
-        <v>2.023844055306275e-11</v>
+        <v>3.035766082959412e-11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="I26" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="U26" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.61907524424502e-13</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.04768811061255e-11</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="H27" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="I27" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="N27" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="O27" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="T27" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="U27" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="AA27" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="H28" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="I28" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="T28" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="U28" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6291,13 +6291,13 @@
         <v>-4.04768811061255e-11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="H29" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="I29" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="N29" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="T29" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="U29" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6419,10 +6419,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="H30" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N30" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="T30" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>-13.84864717531928</v>
+        <v>-13.84864717531923</v>
       </c>
       <c r="F31" t="n">
-        <v>-3462.161793829819</v>
+        <v>-3462.161793829809</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="N31" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="O31" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.00403337029373678</v>
+        <v>0.004033370293736781</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.004536383830931639</v>
+        <v>-0.0045363838309317</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.003546413586379021</v>
+        <v>-0.003546413586378977</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>13.84864717531929</v>
+        <v>13.84864717531926</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>-13.84864717531929</v>
+        <v>-13.84864717531926</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>13.84864717531945</v>
+        <v>13.84864717531942</v>
       </c>
       <c r="F32" t="n">
-        <v>3462.161793829863</v>
+        <v>3462.161793829856</v>
       </c>
       <c r="G32" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="N32" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="O32" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.191049997705368e-18</v>
+        <v>6.8997973204105e-19</v>
       </c>
       <c r="T32" t="n">
-        <v>-1.350523754131053e-18</v>
+        <v>-7.823634774238298e-19</v>
       </c>
       <c r="U32" t="n">
-        <v>1.559450505989095e-18</v>
+        <v>9.033955285895597e-19</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.000296756725185418</v>
+        <v>0.0002967567251854169</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.001808660202981712</v>
+        <v>0.00180866020298177</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.009215880681517451</v>
+        <v>-0.009215880681517411</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>-13.84864717531946</v>
+        <v>-13.84864717531943</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>13.84864717531946</v>
+        <v>13.84864717531943</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>15.48325824021166</v>
+        <v>15.48325824021185</v>
       </c>
       <c r="F33" t="n">
-        <v>3870.814560052914</v>
+        <v>3870.814560052963</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003709459064817539</v>
+        <v>0.0003709459064817586</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.002069028233553033</v>
+        <v>-0.002069028233553117</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-15.48325824021166</v>
+        <v>-15.48325824021185</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>15.48325824021166</v>
+        <v>15.48325824021185</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>-15.48325824021186</v>
+        <v>-15.48325824021206</v>
       </c>
       <c r="F34" t="n">
-        <v>-3870.814560052966</v>
+        <v>-3870.814560053016</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.382099995410737e-18</v>
+        <v>-1.3799594640821e-18</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="O34" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.065307503788069e-18</v>
+        <v>6.171366335763509e-19</v>
       </c>
       <c r="T34" t="n">
-        <v>-2.130615007576138e-18</v>
+        <v>-1.234273267152702e-18</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.0003709459064817577</v>
+        <v>-0.000370945906481763</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.00206902823355303</v>
+        <v>0.002069028233553113</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.005730488065956673</v>
+        <v>-0.00573048806595661</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>15.48325824021186</v>
+        <v>15.48325824021206</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-15.48325824021186</v>
+        <v>-15.48325824021206</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7059,13 +7059,13 @@
         <v>-3462.161793829839</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078549</v>
       </c>
       <c r="H35" t="n">
-        <v>0.001418883819716367</v>
+        <v>0.001418883819716404</v>
       </c>
       <c r="I35" t="n">
-        <v>0.006207015870879487</v>
+        <v>0.006207015870879429</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="N35" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="O35" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.00720700243026396</v>
+        <v>0.007207002430263966</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.006026821925871149</v>
+        <v>-0.006026821925871099</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0001682452488700487</v>
+        <v>0.0001682452488699993</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.006910245705078545</v>
+        <v>0.006910245705078552</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.006281299093253511</v>
+        <v>-0.006281299093253591</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.008038163939427604</v>
+        <v>-0.008038163939427563</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>13.8486471753194</v>
+        <v>13.84864717531934</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>-13.8486471753194</v>
+        <v>-13.84864717531934</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>13.8486471753195</v>
+        <v>13.84864717531946</v>
       </c>
       <c r="F36" t="n">
-        <v>3462.161793829874</v>
+        <v>3462.161793829864</v>
       </c>
       <c r="G36" t="n">
-        <v>0.006910245705078541</v>
+        <v>0.006910245705078548</v>
       </c>
       <c r="H36" t="n">
-        <v>2.449185325768649e-05</v>
+        <v>2.449185325764698e-05</v>
       </c>
       <c r="I36" t="n">
-        <v>0.001292984129120542</v>
+        <v>0.001292984129120605</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="N36" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="O36" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.002876875411341762</v>
+        <v>-0.002876875411341767</v>
       </c>
       <c r="T36" t="n">
-        <v>0.003299098297921221</v>
+        <v>0.003299098297921169</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.005501221846268381</v>
+        <v>-0.005501221846268434</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.002580118686156344</v>
+        <v>-0.00258011868615635</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.005735754367663509</v>
+        <v>0.005735754367663588</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.0118178086695199</v>
+        <v>-0.01181780866951986</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>-13.8486471753195</v>
+        <v>-13.84864717531946</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>13.8486471753195</v>
+        <v>13.84864717531946</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>15.48325824021174</v>
+        <v>15.48325824021193</v>
       </c>
       <c r="F37" t="n">
-        <v>3870.814560052935</v>
+        <v>3870.814560052982</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002016487163610053</v>
+        <v>0.002016487163610129</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0005935134503707814</v>
+        <v>0.0005935134503708136</v>
       </c>
       <c r="I37" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.00143265504295337</v>
+        <v>0.001432655042953433</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.001538173665317224</v>
+        <v>-0.001538173665317278</v>
       </c>
       <c r="U37" t="n">
-        <v>0.005730488065956673</v>
+        <v>0.00573048806595661</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.001803600949435126</v>
+        <v>0.001803600949435193</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.004934338319459721</v>
+        <v>-0.004934338319459988</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-15.48325824021174</v>
+        <v>-15.48325824021192</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>15.48325824021174</v>
+        <v>15.48325824021192</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>-15.48325824021189</v>
+        <v>-15.48325824021211</v>
       </c>
       <c r="F38" t="n">
-        <v>-3870.814560052973</v>
+        <v>-3870.814560053027</v>
       </c>
       <c r="G38" t="n">
-        <v>0.002016487163610054</v>
+        <v>0.002016487163610131</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0005935134503707861</v>
+        <v>-0.0005935134503708194</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0009361786007100264</v>
+        <v>0.0009361786007100936</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="N38" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="O38" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.001432655042953374</v>
+        <v>-0.001432655042953438</v>
       </c>
       <c r="T38" t="n">
-        <v>0.001538173665317223</v>
+        <v>0.001538173665317277</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.0009361786007100264</v>
+        <v>-0.0009361786007100936</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.001803600949435134</v>
+        <v>-0.001803600949435203</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.004934338319459717</v>
+        <v>0.004934338319459983</v>
       </c>
       <c r="AA38" t="n">
-        <v>-0.004269511934043515</v>
+        <v>-0.00426951193404345</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>15.48325824021189</v>
+        <v>15.4832582402121</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-15.48325824021189</v>
+        <v>-15.4832582402121</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>-13.84864717531936</v>
+        <v>-13.84864717531915</v>
       </c>
       <c r="F39" t="n">
-        <v>-3462.161793829839</v>
+        <v>-3462.161793829788</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="H39" t="n">
-        <v>0.001858755894930288</v>
+        <v>0.001858755894930333</v>
       </c>
       <c r="I39" t="n">
-        <v>0.005000000000000101</v>
+        <v>0.005000000000000029</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="N39" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.005368252528551776</v>
+        <v>0.00536825252855185</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.003276851444683088</v>
+        <v>-0.003276851444683104</v>
       </c>
       <c r="U39" t="n">
-        <v>0.0118178086695199</v>
+        <v>0.01181780866951986</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.005071495803366361</v>
+        <v>0.00507149580336644</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.005713507514425355</v>
+        <v>-0.005713507514425525</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.004905638937448047</v>
+        <v>0.004905638937448285</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>13.84864717531937</v>
+        <v>13.84864717531914</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>-13.84864717531937</v>
+        <v>-13.84864717531914</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>13.84864717531956</v>
+        <v>13.84864717531931</v>
       </c>
       <c r="F40" t="n">
-        <v>3462.16179382989</v>
+        <v>3462.161793829829</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0122784982336304</v>
+        <v>0.01227849823363042</v>
       </c>
       <c r="H40" t="n">
-        <v>0.001027995451017834</v>
+        <v>0.001027995451017786</v>
       </c>
       <c r="I40" t="n">
-        <v>-6.752144827409786e-17</v>
+        <v>6.98034996549076e-18</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="N40" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="O40" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.005368252528551795</v>
+        <v>-0.005368252528551873</v>
       </c>
       <c r="T40" t="n">
-        <v>0.007641209249402946</v>
+        <v>0.007641209249402963</v>
       </c>
       <c r="U40" t="n">
-        <v>0.008038163939427604</v>
+        <v>0.008038163939427563</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.005071495803366376</v>
+        <v>-0.005071495803366459</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.007895686416785296</v>
+        <v>0.007895686416785464</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.003015816572401887</v>
+        <v>0.003015816572402124</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>-13.84864717531957</v>
+        <v>-13.84864717531931</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>13.84864717531957</v>
+        <v>13.84864717531931</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>15.48325824021191</v>
+        <v>15.48325824021209</v>
       </c>
       <c r="F41" t="n">
-        <v>3870.814560052978</v>
+        <v>3870.814560053023</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="H41" t="n">
-        <v>0.000593513450370752</v>
+        <v>0.0005935134503708089</v>
       </c>
       <c r="I41" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N41" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.002865310085906693</v>
+        <v>0.002865310085906864</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.004403483751223937</v>
+        <v>-0.004403483751224152</v>
       </c>
       <c r="U41" t="n">
-        <v>0.004269511934043515</v>
+        <v>0.00426951193404345</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.003236255992388453</v>
+        <v>0.003236255992388629</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.006472511984776729</v>
+        <v>-0.00647251198477725</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-15.48325824021192</v>
+        <v>-15.48325824021209</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>15.48325824021192</v>
+        <v>15.48325824021209</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>-15.48325824021211</v>
+        <v>-15.48325824021231</v>
       </c>
       <c r="F42" t="n">
-        <v>-3870.814560053027</v>
+        <v>-3870.814560053077</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005220001227961625</v>
+        <v>0.005220001227961893</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.0005935134503707612</v>
+        <v>-0.00059351345037082</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0009361786007101457</v>
+        <v>-0.0009361786007100781</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N42" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.002865310085906701</v>
+        <v>-0.002865310085906874</v>
       </c>
       <c r="T42" t="n">
-        <v>0.004403483751223933</v>
+        <v>0.004403483751224147</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0009361786007101457</v>
+        <v>0.0009361786007100781</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.003236255992388466</v>
+        <v>-0.003236255992388644</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.006472511984776723</v>
+        <v>0.006472511984777243</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>15.48325824021211</v>
+        <v>15.48325824021231</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-15.48325824021211</v>
+        <v>-15.48325824021231</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>-13.84864717531942</v>
+        <v>-13.84864717531917</v>
       </c>
       <c r="F43" t="n">
-        <v>-3462.161793829854</v>
+        <v>-3462.161793829794</v>
       </c>
       <c r="G43" t="n">
-        <v>0.008986496724337585</v>
+        <v>0.008986496724337876</v>
       </c>
       <c r="H43" t="n">
-        <v>0.001418883819716362</v>
+        <v>0.001418883819716412</v>
       </c>
       <c r="I43" t="n">
-        <v>0.003792984129120687</v>
+        <v>0.003792984129120626</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N43" t="n">
-        <v>7.947928030001671e-17</v>
+        <v>2.947134575969546e-18</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.003915000920971208</v>
+        <v>0.003915000920971418</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.00229404307905491</v>
+        <v>-0.002294043079055072</v>
       </c>
       <c r="U43" t="n">
-        <v>0.008750269562383738</v>
+        <v>0.008750269562383884</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.003618244195785792</v>
+        <v>0.003618244195786007</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.004102703282036496</v>
+        <v>-0.004102703282036856</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.004737393688577926</v>
+        <v>0.004737393688578282</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>13.84864717531943</v>
+        <v>13.84864717531917</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-13.84864717531943</v>
+        <v>-13.84864717531917</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>13.84864717531956</v>
+        <v>13.84864717531934</v>
       </c>
       <c r="F44" t="n">
-        <v>3462.16179382989</v>
+        <v>3462.161793829834</v>
       </c>
       <c r="G44" t="n">
-        <v>0.008986496724337583</v>
+        <v>0.008986496724337874</v>
       </c>
       <c r="H44" t="n">
-        <v>2.44918532577016e-05</v>
+        <v>2.449185325764975e-05</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.001292984129120654</v>
+        <v>-0.001292984129120591</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.007236488391571465</v>
+        <v>0.00723648839157201</v>
       </c>
       <c r="N44" t="n">
-        <v>-9.340821653536937e-17</v>
+        <v>-2.002412356229263e-17</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.003915000920971222</v>
+        <v>-0.003915000920971435</v>
       </c>
       <c r="T44" t="n">
-        <v>0.004476221981414849</v>
+        <v>0.00447622198141501</v>
       </c>
       <c r="U44" t="n">
-        <v>0.006860447197337577</v>
+        <v>0.00686044719733772</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>-0.003618244195785803</v>
+        <v>-0.00361824419578602</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.004102703282036487</v>
+        <v>0.004102703282036844</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.004737393688577926</v>
+        <v>0.004737393688578282</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-13.84864717531957</v>
+        <v>-13.84864717531934</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>13.84864717531957</v>
+        <v>13.84864717531934</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_supp_disp.xlsx
+++ b/outputs/validation_truss_supp_disp.xlsx
@@ -538,7 +538,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -556,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3799594640821e-18</v>
+        <v>2.382099995410737e-18</v>
       </c>
     </row>
     <row r="4">
@@ -573,13 +573,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -591,7 +591,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00939637020448634</v>
+        <v>0.009396370204486366</v>
       </c>
     </row>
     <row r="5">
@@ -608,13 +608,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="F5" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -626,7 +626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007030213617920176</v>
+        <v>0.007030213617920157</v>
       </c>
     </row>
     <row r="6">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.006103848963633243</v>
+        <v>0.006103848963633275</v>
       </c>
     </row>
     <row r="7">
@@ -678,13 +678,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002301066941486712</v>
+        <v>0.002301066941486609</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="G9" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -766,7 +766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01232145663144494</v>
+        <v>0.01232145663144493</v>
       </c>
     </row>
     <row r="10">
@@ -783,13 +783,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.006769741737365922</v>
+        <v>0.006769741737365751</v>
       </c>
     </row>
     <row r="11">
@@ -818,13 +818,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.005336394045432011</v>
+        <v>0.005336394045431754</v>
       </c>
     </row>
     <row r="12">
@@ -853,13 +853,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E12" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="F12" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -871,7 +871,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.009856829270822811</v>
+        <v>0.009856829270822563</v>
       </c>
     </row>
     <row r="13">
@@ -888,13 +888,13 @@
         <v>2.598076211353316</v>
       </c>
       <c r="E13" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="F13" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.009079071053008071</v>
+        <v>0.009079071053007792</v>
       </c>
     </row>
     <row r="14">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
     </row>
     <row r="15">
@@ -958,10 +958,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="F15" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
     </row>
   </sheetData>
@@ -1038,13 +1038,13 @@
         <v>0.01338717641439762</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
     </row>
     <row r="3">
@@ -1057,16 +1057,16 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="F3" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
     </row>
     <row r="4">
@@ -1079,16 +1079,16 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
     </row>
     <row r="5">
@@ -1154,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.700062395888381e-13</v>
+        <v>4.831690603168681e-13</v>
       </c>
       <c r="C2" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>2.728484105318785e-12</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98656052374821</v>
+        <v>23.98656052374835</v>
       </c>
     </row>
     <row r="3">
@@ -1169,10 +1169,10 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-8.242295734817162e-13</v>
+        <v>-2.700062395888381e-12</v>
       </c>
       <c r="D3" t="n">
-        <v>-23.98656052374844</v>
+        <v>-23.98656052374853</v>
       </c>
     </row>
     <row r="4">
@@ -1182,7 +1182,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-23.98656052374835</v>
+        <v>-23.98656052374873</v>
       </c>
     </row>
     <row r="5">
@@ -1192,7 +1192,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>23.98656052374813</v>
+        <v>23.98656052374851</v>
       </c>
     </row>
   </sheetData>
@@ -1275,16 +1275,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="G2" t="n">
-        <v>9.891890839513561e-05</v>
+        <v>9.891890839513024e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>27.69729435063797</v>
+        <v>27.69729435063647</v>
       </c>
       <c r="I2" t="n">
-        <v>6924.323587659492</v>
+        <v>6924.323587659116</v>
       </c>
     </row>
     <row r="3">
@@ -1306,16 +1306,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0006677026316671804</v>
+        <v>-0.0006677026316671839</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001284994313772227</v>
+        <v>-0.0001284994313772234</v>
       </c>
       <c r="H3" t="n">
-        <v>-35.97984078562236</v>
+        <v>-35.97984078562255</v>
       </c>
       <c r="I3" t="n">
-        <v>-8994.960196405589</v>
+        <v>-8994.960196405636</v>
       </c>
     </row>
     <row r="4">
@@ -1337,16 +1337,16 @@
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>2.602085213965211e-18</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="G4" t="n">
-        <v>8.673617379884035e-19</v>
+        <v>-2.891205793294678e-19</v>
       </c>
       <c r="H4" t="n">
-        <v>2.42861286636753e-13</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="I4" t="n">
-        <v>6.071532165918825e-11</v>
+        <v>-2.023844055306275e-11</v>
       </c>
     </row>
     <row r="5">
@@ -1399,16 +1399,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.734723475976807e-18</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.891205793294678e-19</v>
+        <v>-1.445602896647339e-19</v>
       </c>
       <c r="H6" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>-1.011922027653137e-11</v>
       </c>
     </row>
     <row r="7">
@@ -1430,16 +1430,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.662069341687669e-18</v>
+        <v>-2.938187887435717e-17</v>
       </c>
       <c r="G7" t="n">
-        <v>-7.770115569479449e-19</v>
+        <v>-4.896979812392861e-18</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.175632359454245e-13</v>
+        <v>-1.371154347470001e-12</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.439080898635613e-11</v>
+        <v>-3.427885868675003e-10</v>
       </c>
     </row>
     <row r="8">
@@ -1461,16 +1461,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.602085213965211e-18</v>
+        <v>-2.168404344971009e-18</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.336808689942018e-19</v>
+        <v>-3.614007241618348e-19</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.214306433183765e-13</v>
+        <v>-1.011922027653137e-13</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.035766082959412e-11</v>
+        <v>-2.529805069132843e-11</v>
       </c>
     </row>
     <row r="9">
@@ -1492,16 +1492,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0002225675438890656</v>
+        <v>0.0002225675438890678</v>
       </c>
       <c r="G9" t="n">
-        <v>4.283314379240863e-05</v>
+        <v>4.283314379240905e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>11.99328026187442</v>
+        <v>11.99328026187453</v>
       </c>
       <c r="I9" t="n">
-        <v>2998.320065468604</v>
+        <v>2998.320065468633</v>
       </c>
     </row>
     <row r="10">
@@ -1554,16 +1554,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.000593513450370829</v>
+        <v>-0.0005935134503708455</v>
       </c>
       <c r="G11" t="n">
-        <v>-9.891890839513817e-05</v>
+        <v>-9.891890839514092e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>-27.69729435063869</v>
+        <v>-27.69729435063945</v>
       </c>
       <c r="I11" t="n">
-        <v>-6924.323587659671</v>
+        <v>-6924.323587659863</v>
       </c>
     </row>
     <row r="12">
@@ -1585,16 +1585,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0006677026316671839</v>
+        <v>0.0006677026316671939</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0001284994313772234</v>
+        <v>0.0001284994313772253</v>
       </c>
       <c r="H12" t="n">
-        <v>35.97984078562255</v>
+        <v>35.97984078562308</v>
       </c>
       <c r="I12" t="n">
-        <v>8994.960196405636</v>
+        <v>8994.960196405771</v>
       </c>
     </row>
     <row r="13">
@@ -1616,16 +1616,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.891890839513655e-05</v>
+        <v>-9.891890839513101e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>-27.69729435063823</v>
+        <v>-27.69729435063668</v>
       </c>
       <c r="I13" t="n">
-        <v>-6924.323587659558</v>
+        <v>-6924.323587659171</v>
       </c>
     </row>
     <row r="14">
@@ -1647,16 +1647,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0006677026316671856</v>
+        <v>0.0006677026316671881</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001284994313772237</v>
+        <v>0.0001284994313772242</v>
       </c>
       <c r="H14" t="n">
-        <v>35.97984078562264</v>
+        <v>35.97984078562278</v>
       </c>
       <c r="I14" t="n">
-        <v>8994.96019640566</v>
+        <v>8994.960196405695</v>
       </c>
     </row>
     <row r="15">
@@ -1678,16 +1678,16 @@
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>6.505213034913027e-19</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.168404344971009e-19</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>6.071532165918825e-14</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1.517883041479706e-11</v>
       </c>
     </row>
     <row r="16">
@@ -1709,16 +1709,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0002225675438890622</v>
+        <v>0.0002225675438890636</v>
       </c>
       <c r="G16" t="n">
-        <v>4.283314379240796e-05</v>
+        <v>4.283314379240823e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>11.99328026187423</v>
+        <v>11.99328026187431</v>
       </c>
       <c r="I16" t="n">
-        <v>2998.320065468557</v>
+        <v>2998.320065468577</v>
       </c>
     </row>
     <row r="17">
@@ -1740,16 +1740,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>-1.084202172485504e-19</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.445602896647339e-19</v>
+        <v>-1.807003620809174e-20</v>
       </c>
       <c r="H17" t="n">
-        <v>-4.04768811061255e-14</v>
+        <v>-5.059610138265687e-15</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.011922027653137e-11</v>
+        <v>-1.264902534566422e-12</v>
       </c>
     </row>
     <row r="18">
@@ -1771,16 +1771,16 @@
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.505213034913027e-19</v>
+        <v>2.482822974991805e-17</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.084202172485504e-19</v>
+        <v>4.138038291653008e-18</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.035766082959412e-14</v>
+        <v>1.158650721662842e-12</v>
       </c>
       <c r="I18" t="n">
-        <v>-7.589415207398531e-12</v>
+        <v>2.896626804157106e-10</v>
       </c>
     </row>
     <row r="19">
@@ -1802,16 +1802,16 @@
         <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>-7.589415207398531e-19</v>
+        <v>-1.192622389734055e-18</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.264902534566422e-19</v>
+        <v>-1.987703982890091e-19</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.541727096785981e-14</v>
+        <v>-5.565571152092256e-14</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.854317741964952e-12</v>
+        <v>-1.391392788023064e-11</v>
       </c>
     </row>
     <row r="20">
@@ -1833,16 +1833,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0002225675438890598</v>
+        <v>-0.0002225675438890618</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.28331437924075e-05</v>
+        <v>-4.28331437924079e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>-11.9932802618741</v>
+        <v>-11.99328026187421</v>
       </c>
       <c r="I20" t="n">
-        <v>-2998.320065468525</v>
+        <v>-2998.320065468553</v>
       </c>
     </row>
     <row r="21">
@@ -1864,16 +1864,16 @@
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2.891205793294678e-19</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.023844055306275e-11</v>
       </c>
     </row>
     <row r="22">
@@ -1895,16 +1895,16 @@
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0005935134503708229</v>
+        <v>0.0005935134503708407</v>
       </c>
       <c r="G22" t="n">
-        <v>9.891890839513715e-05</v>
+        <v>9.891890839514012e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>27.6972943506384</v>
+        <v>27.69729435063923</v>
       </c>
       <c r="I22" t="n">
-        <v>6924.3235876596</v>
+        <v>6924.323587659808</v>
       </c>
     </row>
     <row r="23">
@@ -1926,16 +1926,16 @@
         <v>5.196152422706632</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0006677026316671785</v>
+        <v>-0.0006677026316671884</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0001284994313772223</v>
+        <v>-0.0001284994313772243</v>
       </c>
       <c r="H23" t="n">
-        <v>-35.97984078562226</v>
+        <v>-35.97984078562279</v>
       </c>
       <c r="I23" t="n">
-        <v>-8994.960196405564</v>
+        <v>-8994.960196405698</v>
       </c>
     </row>
     <row r="24">
@@ -1957,16 +1957,16 @@
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.599864880273667e-19</v>
+        <v>-7.94033331803579e-19</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.287962166476626e-13</v>
+        <v>-2.223293329050021e-13</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.219905416191566e-11</v>
+        <v>-5.558233322625052e-11</v>
       </c>
     </row>
     <row r="25">
@@ -1988,16 +1988,16 @@
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.673617379884035e-19</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.891205793294678e-19</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2019,16 +2019,16 @@
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1.301042606982605e-18</v>
+        <v>8.673617379884035e-19</v>
       </c>
       <c r="G26" t="n">
-        <v>4.336808689942018e-19</v>
+        <v>2.891205793294678e-19</v>
       </c>
       <c r="H26" t="n">
-        <v>1.214306433183765e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="I26" t="n">
-        <v>3.035766082959412e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
     </row>
     <row r="27">
@@ -2050,16 +2050,16 @@
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-1.734723475976807e-18</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-5.782411586589357e-19</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-4.04768811061255e-11</v>
       </c>
     </row>
     <row r="28">
@@ -2174,16 +2174,16 @@
         <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0002967567251854122</v>
+        <v>-0.000296756725185413</v>
       </c>
       <c r="G31" t="n">
-        <v>-4.94594541975687e-05</v>
+        <v>-4.945945419756884e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>-13.84864717531923</v>
+        <v>-13.84864717531928</v>
       </c>
       <c r="I31" t="n">
-        <v>-3462.161793829809</v>
+        <v>-3462.161793829819</v>
       </c>
     </row>
     <row r="32">
@@ -2205,16 +2205,16 @@
         <v>6</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0002967567251854162</v>
+        <v>0.0002967567251854168</v>
       </c>
       <c r="G32" t="n">
-        <v>4.945945419756938e-05</v>
+        <v>4.945945419756947e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>13.84864717531942</v>
+        <v>13.84864717531945</v>
       </c>
       <c r="I32" t="n">
-        <v>3462.161793829856</v>
+        <v>3462.161793829863</v>
       </c>
     </row>
     <row r="33">
@@ -2236,16 +2236,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0003709459064817586</v>
+        <v>0.0003709459064817539</v>
       </c>
       <c r="G33" t="n">
-        <v>5.529735085789947e-05</v>
+        <v>5.529735085789877e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>15.48325824021185</v>
+        <v>15.48325824021166</v>
       </c>
       <c r="I33" t="n">
-        <v>3870.814560052963</v>
+        <v>3870.814560052914</v>
       </c>
     </row>
     <row r="34">
@@ -2267,16 +2267,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0003709459064817636</v>
+        <v>-0.0003709459064817588</v>
       </c>
       <c r="G34" t="n">
-        <v>-5.529735085790022e-05</v>
+        <v>-5.52973508578995e-05</v>
       </c>
       <c r="H34" t="n">
-        <v>-15.48325824021206</v>
+        <v>-15.48325824021186</v>
       </c>
       <c r="I34" t="n">
-        <v>-3870.814560053016</v>
+        <v>-3870.814560052966</v>
       </c>
     </row>
     <row r="35">
@@ -2329,16 +2329,16 @@
         <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0002967567251854169</v>
+        <v>0.0002967567251854178</v>
       </c>
       <c r="G36" t="n">
-        <v>4.945945419756949e-05</v>
+        <v>4.945945419756963e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>13.84864717531946</v>
+        <v>13.8486471753195</v>
       </c>
       <c r="I36" t="n">
-        <v>3462.161793829864</v>
+        <v>3462.161793829874</v>
       </c>
     </row>
     <row r="37">
@@ -2360,16 +2360,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0003709459064817604</v>
+        <v>0.0003709459064817559</v>
       </c>
       <c r="G37" t="n">
-        <v>5.529735085789974e-05</v>
+        <v>5.529735085789907e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>15.48325824021193</v>
+        <v>15.48325824021174</v>
       </c>
       <c r="I37" t="n">
-        <v>3870.814560052982</v>
+        <v>3870.814560052935</v>
       </c>
     </row>
     <row r="38">
@@ -2391,16 +2391,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.0003709459064817648</v>
+        <v>-0.0003709459064817596</v>
       </c>
       <c r="G38" t="n">
-        <v>-5.529735085790039e-05</v>
+        <v>-5.529735085789961e-05</v>
       </c>
       <c r="H38" t="n">
-        <v>-15.48325824021211</v>
+        <v>-15.48325824021189</v>
       </c>
       <c r="I38" t="n">
-        <v>-3870.814560053027</v>
+        <v>-3870.814560052973</v>
       </c>
     </row>
     <row r="39">
@@ -2422,16 +2422,16 @@
         <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.0002967567251854104</v>
+        <v>-0.0002967567251854148</v>
       </c>
       <c r="G39" t="n">
-        <v>-4.945945419756841e-05</v>
+        <v>-4.945945419756913e-05</v>
       </c>
       <c r="H39" t="n">
-        <v>-13.84864717531915</v>
+        <v>-13.84864717531936</v>
       </c>
       <c r="I39" t="n">
-        <v>-3462.161793829788</v>
+        <v>-3462.161793829839</v>
       </c>
     </row>
     <row r="40">
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0002967567251854139</v>
+        <v>0.0002967567251854191</v>
       </c>
       <c r="G40" t="n">
-        <v>4.945945419756898e-05</v>
+        <v>4.945945419756985e-05</v>
       </c>
       <c r="H40" t="n">
-        <v>13.84864717531931</v>
+        <v>13.84864717531956</v>
       </c>
       <c r="I40" t="n">
-        <v>3462.161793829829</v>
+        <v>3462.16179382989</v>
       </c>
     </row>
     <row r="41">
@@ -2484,16 +2484,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0003709459064817643</v>
+        <v>0.00037094590648176</v>
       </c>
       <c r="G41" t="n">
-        <v>5.529735085790033e-05</v>
+        <v>5.529735085789968e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>15.48325824021209</v>
+        <v>15.48325824021191</v>
       </c>
       <c r="I41" t="n">
-        <v>3870.814560053023</v>
+        <v>3870.814560052978</v>
       </c>
     </row>
     <row r="42">
@@ -2515,16 +2515,16 @@
         <v>6.708203932499369</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.0003709459064817696</v>
+        <v>-0.0003709459064817648</v>
       </c>
       <c r="G42" t="n">
-        <v>-5.529735085790111e-05</v>
+        <v>-5.529735085790039e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>-15.48325824021231</v>
+        <v>-15.48325824021211</v>
       </c>
       <c r="I42" t="n">
-        <v>-3870.814560053077</v>
+        <v>-3870.814560053027</v>
       </c>
     </row>
     <row r="43">
@@ -2546,16 +2546,16 @@
         <v>6</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.0002967567251854109</v>
+        <v>-0.0002967567251854161</v>
       </c>
       <c r="G43" t="n">
-        <v>-4.945945419756848e-05</v>
+        <v>-4.945945419756935e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>-13.84864717531917</v>
+        <v>-13.84864717531942</v>
       </c>
       <c r="I43" t="n">
-        <v>-3462.161793829794</v>
+        <v>-3462.161793829854</v>
       </c>
     </row>
     <row r="44">
@@ -2577,16 +2577,16 @@
         <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0002967567251854143</v>
+        <v>0.0002967567251854191</v>
       </c>
       <c r="G44" t="n">
-        <v>4.945945419756906e-05</v>
+        <v>4.945945419756985e-05</v>
       </c>
       <c r="H44" t="n">
-        <v>13.84864717531934</v>
+        <v>13.84864717531956</v>
       </c>
       <c r="I44" t="n">
-        <v>3462.161793829834</v>
+        <v>3462.16179382989</v>
       </c>
     </row>
   </sheetData>
@@ -2829,10 +2829,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>27.69729435063797</v>
+        <v>27.69729435063647</v>
       </c>
       <c r="F2" t="n">
-        <v>6924.323587659492</v>
+        <v>6924.323587659116</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2853,13 +2853,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -2889,13 +2889,13 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.002016487163610129</v>
+        <v>-0.002016487163610053</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-27.69729435063797</v>
+        <v>-27.69729435063647</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>27.69729435063797</v>
+        <v>27.69729435063647</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -2957,10 +2957,10 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E3" t="n">
-        <v>-35.97984078562236</v>
+        <v>-35.97984078562255</v>
       </c>
       <c r="F3" t="n">
-        <v>-8994.960196405589</v>
+        <v>-8994.960196405636</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -3017,13 +3017,13 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.00433229736833282</v>
+        <v>0.004332297368332816</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.004665991516016574</v>
+        <v>-0.004665991516016643</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.006910245705078549</v>
+        <v>-0.006910245705078541</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>35.97984078562237</v>
+        <v>35.97984078562254</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-35.97984078562237</v>
+        <v>-35.97984078562254</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3085,19 +3085,19 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2.42861286636753e-13</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="F4" t="n">
-        <v>6.071532165918825e-11</v>
+        <v>-2.023844055306275e-11</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -3109,13 +3109,13 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.004665991516016575</v>
+        <v>-0.004665991516016644</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00433229736833282</v>
+        <v>0.004332297368332817</v>
       </c>
       <c r="U4" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3145,13 +3145,13 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.004665991516016573</v>
+        <v>-0.004665991516016645</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003379241758487184</v>
+        <v>0.003379241758487188</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3219,13 +3219,13 @@
         <v>-2998.320065468499</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -3237,13 +3237,13 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="N5" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="O5" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.00433229736833282</v>
+        <v>0.004332297368332816</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.004665991516016574</v>
+        <v>-0.004665991516016643</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.006910245705078549</v>
+        <v>-0.006910245705078541</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.004109729824443762</v>
+        <v>0.004109729824443758</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.003400749071457051</v>
+        <v>-0.003400749071457136</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.01227849823363042</v>
+        <v>-0.0122784982336304</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>11.99328026187399</v>
+        <v>11.99328026187402</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-11.99328026187399</v>
+        <v>-11.99328026187402</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3341,19 +3341,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>-1.011922027653137e-11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -3365,13 +3365,13 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.005259504966387387</v>
+        <v>0.005259504966387426</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.002351246307469425</v>
+        <v>-0.002351246307469485</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.002016487163610129</v>
+        <v>-0.002016487163610053</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -3401,13 +3401,13 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.005259504966387385</v>
+        <v>0.005259504966387425</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0008902701755562667</v>
+        <v>-0.0008902701755563423</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.01227849823363042</v>
+        <v>-0.0122784982336304</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -3469,19 +3469,19 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.175632359454245e-13</v>
+        <v>-1.371154347470001e-12</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.439080898635613e-11</v>
+        <v>-3.427885868675003e-10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -3493,13 +3493,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.002016487163610129</v>
+        <v>-0.002016487163610053</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -3529,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="Z7" t="n">
-        <v>-0.005220001227961893</v>
+        <v>-0.005220001227961625</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.167155344068306e-13</v>
+        <v>1.371347480016993e-12</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-2.167155344068306e-13</v>
+        <v>-1.371347480016993e-12</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3597,19 +3597,19 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.214306433183765e-13</v>
+        <v>-1.011922027653137e-13</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.035766082959412e-11</v>
+        <v>-2.529805069132843e-11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -3639,13 +3639,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.003400749071457052</v>
+        <v>-0.003400749071457137</v>
       </c>
       <c r="T8" t="n">
-        <v>0.004109729824443762</v>
+        <v>0.004109729824443758</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -3657,13 +3657,13 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>-0.003400749071457054</v>
+        <v>-0.003400749071457139</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0026487536925306</v>
+        <v>0.002648753692530583</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3725,19 +3725,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E9" t="n">
-        <v>11.99328026187442</v>
+        <v>11.99328026187453</v>
       </c>
       <c r="F9" t="n">
-        <v>2998.320065468604</v>
+        <v>2998.320065468633</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -3749,13 +3749,13 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="N9" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -3767,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0008902701755562669</v>
+        <v>-0.0008902701755563425</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005259504966387384</v>
+        <v>0.005259504966387424</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0006677026316672012</v>
+        <v>-0.0006677026316672747</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.003994262521827863</v>
+        <v>0.003994262521827891</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-11.99328026187442</v>
+        <v>-11.99328026187453</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -3821,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>11.99328026187442</v>
+        <v>11.99328026187453</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -3859,13 +3859,13 @@
         <v>2.023844055306275e-11</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -3877,13 +3877,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="N10" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="O10" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.003994262521827863</v>
+        <v>0.003994262521827891</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.00162075824151285</v>
+        <v>-0.001620758241512932</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.005220001227961893</v>
+        <v>-0.005220001227961625</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -3913,13 +3913,13 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.003994262521827864</v>
+        <v>0.003994262521827892</v>
       </c>
       <c r="Z10" t="n">
-        <v>-0.000667702631667201</v>
+        <v>-0.0006677026316672745</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.008986496724337876</v>
+        <v>-0.008986496724337585</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -3981,19 +3981,19 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>-27.69729435063869</v>
+        <v>-27.69729435063945</v>
       </c>
       <c r="F11" t="n">
-        <v>-6924.323587659671</v>
+        <v>-6924.323587659863</v>
       </c>
       <c r="G11" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -4005,10 +4005,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.005220001227961893</v>
+        <v>-0.005220001227961625</v>
       </c>
       <c r="U11" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -4041,10 +4041,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="Z11" t="n">
-        <v>-0.00723648839157201</v>
+        <v>-0.007236488391571465</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>27.69729435063869</v>
+        <v>27.69729435063946</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-27.69729435063869</v>
+        <v>-27.69729435063946</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4109,19 +4109,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E12" t="n">
-        <v>35.97984078562255</v>
+        <v>35.97984078562308</v>
       </c>
       <c r="F12" t="n">
-        <v>8994.960196405636</v>
+        <v>8994.960196405771</v>
       </c>
       <c r="G12" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="H12" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="I12" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -4151,13 +4151,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0006677026316672012</v>
+        <v>-0.0006677026316672747</v>
       </c>
       <c r="T12" t="n">
-        <v>0.003994262521827863</v>
+        <v>0.003994262521827891</v>
       </c>
       <c r="U12" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -4169,13 +4169,13 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-1.734139969346397e-17</v>
+        <v>-8.089388844182754e-17</v>
       </c>
       <c r="Z12" t="n">
-        <v>-1.001206178114632e-17</v>
+        <v>-4.670410826768469e-17</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-35.97984078562254</v>
+        <v>-35.97984078562309</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>35.97984078562254</v>
+        <v>35.97984078562309</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4237,13 +4237,13 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>-27.69729435063823</v>
+        <v>-27.69729435063668</v>
       </c>
       <c r="F13" t="n">
-        <v>-6924.323587659558</v>
+        <v>-6924.323587659171</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -4261,13 +4261,13 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3799594640821e-18</v>
+        <v>2.382099995410737e-18</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -4297,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="Z13" t="n">
-        <v>-0.002016487163610131</v>
+        <v>-0.002016487163610054</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>27.69729435063824</v>
+        <v>27.69729435063669</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-27.69729435063824</v>
+        <v>-27.69729435063669</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4365,13 +4365,13 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E14" t="n">
-        <v>35.97984078562264</v>
+        <v>35.97984078562278</v>
       </c>
       <c r="F14" t="n">
-        <v>8994.96019640566</v>
+        <v>8994.960196405695</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -4389,13 +4389,13 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="N14" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3799594640821e-18</v>
+        <v>2.382099995410737e-18</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -4425,13 +4425,13 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0006677026316671856</v>
+        <v>0.0006677026316671881</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.001107511175879719</v>
+        <v>-0.001107511175879645</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0.006910245705078548</v>
+        <v>-0.006910245705078541</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-35.97984078562264</v>
+        <v>-35.97984078562278</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>35.97984078562264</v>
+        <v>35.97984078562278</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -4493,19 +4493,19 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>6.071532165918825e-14</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.517883041479706e-11</v>
       </c>
       <c r="G15" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="H15" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -4517,13 +4517,13 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -4535,13 +4535,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.001107511175879719</v>
+        <v>-0.001107511175879645</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0006677026316671856</v>
+        <v>0.0006677026316671881</v>
       </c>
       <c r="U15" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.001107511175879719</v>
+        <v>-0.001107511175879644</v>
       </c>
       <c r="Z15" t="n">
-        <v>-4.590842515383748e-05</v>
+        <v>-4.590842515384225e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4621,19 +4621,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E16" t="n">
-        <v>11.99328026187423</v>
+        <v>11.99328026187431</v>
       </c>
       <c r="F16" t="n">
-        <v>2998.320065468557</v>
+        <v>2998.320065468577</v>
       </c>
       <c r="G16" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="H16" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="N16" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="O16" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -4663,13 +4663,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0006677026316671856</v>
+        <v>0.0006677026316671881</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.001107511175879719</v>
+        <v>-0.001107511175879645</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.006910245705078548</v>
+        <v>-0.006910245705078541</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -4681,13 +4681,13 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.0008902701755562478</v>
+        <v>0.0008902701755562517</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.000513997725508887</v>
+        <v>0.0005139977255089752</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0.01227849823363042</v>
+        <v>-0.0122784982336304</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-11.99328026187423</v>
+        <v>-11.9932802618743</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>11.99328026187423</v>
+        <v>11.9932802618743</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4749,19 +4749,19 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.04768811061255e-14</v>
+        <v>-5.059610138265687e-15</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.011922027653137e-11</v>
+        <v>-1.264902534566422e-12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -4773,13 +4773,13 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="N17" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="O17" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -4791,13 +4791,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0005139977255089</v>
+        <v>0.0005139977255088585</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0009820870258639312</v>
+        <v>-0.0009820870258638687</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.002016487163610131</v>
+        <v>-0.002016487163610054</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.0005139977255088991</v>
+        <v>0.0005139977255088584</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.000890270175556241</v>
+        <v>0.0008902701755563192</v>
       </c>
       <c r="AA17" t="n">
-        <v>-0.01227849823363042</v>
+        <v>-0.0122784982336304</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.907985046680551e-14</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-3.907985046680551e-14</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4877,19 +4877,19 @@
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.035766082959412e-14</v>
+        <v>1.158650721662842e-12</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.589415207398531e-12</v>
+        <v>2.896626804157106e-10</v>
       </c>
       <c r="G18" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -4901,13 +4901,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -4919,13 +4919,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.002016487163610131</v>
+        <v>-0.002016487163610054</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4937,13 +4937,13 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="Z18" t="n">
-        <v>-0.005220001227961893</v>
+        <v>-0.005220001227961625</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>-1.158184659288963e-12</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>1.158184659288963e-12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5005,19 +5005,19 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.541727096785981e-14</v>
+        <v>-5.565571152092256e-14</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.854317741964952e-12</v>
+        <v>-1.391392788023064e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="H19" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="I19" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -5047,13 +5047,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.000513997725508887</v>
+        <v>0.0005139977255089752</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0008902701755562479</v>
+        <v>0.0008902701755562518</v>
       </c>
       <c r="U19" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -5065,13 +5065,13 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.0005139977255088862</v>
+        <v>0.0005139977255089741</v>
       </c>
       <c r="Z19" t="n">
-        <v>-0.0009820870258639238</v>
+        <v>-0.0009820870258639069</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.552713678800501e-14</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-3.552713678800501e-14</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5133,19 +5133,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E20" t="n">
-        <v>-11.9932802618741</v>
+        <v>-11.99328026187421</v>
       </c>
       <c r="F20" t="n">
-        <v>-2998.320065468525</v>
+        <v>-2998.320065468553</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="H20" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="I20" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -5157,13 +5157,13 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="N20" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -5175,13 +5175,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0008902701755562408</v>
+        <v>0.0008902701755563191</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0005139977255088991</v>
+        <v>0.0005139977255088584</v>
       </c>
       <c r="U20" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.0006677026316671811</v>
+        <v>0.0006677026316672573</v>
       </c>
       <c r="Z20" t="n">
-        <v>-0.001107511175879706</v>
+        <v>-0.001107511175879734</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>11.99328026187411</v>
+        <v>11.99328026187421</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -5229,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>-11.99328026187411</v>
+        <v>-11.99328026187421</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -5261,19 +5261,19 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2.023844055306275e-11</v>
       </c>
       <c r="G21" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -5285,13 +5285,13 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="N21" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.001107511175879706</v>
+        <v>-0.001107511175879735</v>
       </c>
       <c r="T21" t="n">
-        <v>-4.590842515384577e-05</v>
+        <v>-4.590842515376115e-05</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.005220001227961893</v>
+        <v>-0.005220001227961625</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -5321,13 +5321,13 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>-0.001107511175879706</v>
+        <v>-0.001107511175879734</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.0006677026316671811</v>
+        <v>0.0006677026316672573</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.008986496724337874</v>
+        <v>-0.008986496724337583</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5389,19 +5389,19 @@
         <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>27.6972943506384</v>
+        <v>27.69729435063923</v>
       </c>
       <c r="F22" t="n">
-        <v>6924.3235876596</v>
+        <v>6924.323587659808</v>
       </c>
       <c r="G22" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -5413,10 +5413,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N22" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -5431,13 +5431,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.005220001227961893</v>
+        <v>-0.005220001227961625</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -5449,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="Z22" t="n">
-        <v>-0.00723648839157201</v>
+        <v>-0.007236488391571465</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-27.69729435063841</v>
+        <v>-27.69729435063924</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>27.69729435063841</v>
+        <v>27.69729435063924</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5517,19 +5517,19 @@
         <v>5.196152422706632</v>
       </c>
       <c r="E23" t="n">
-        <v>-35.97984078562226</v>
+        <v>-35.97984078562279</v>
       </c>
       <c r="F23" t="n">
-        <v>-8994.960196405564</v>
+        <v>-8994.960196405698</v>
       </c>
       <c r="G23" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="H23" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -5541,10 +5541,10 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N23" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -5559,13 +5559,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0006677026316671811</v>
+        <v>0.0006677026316672573</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.001107511175879706</v>
+        <v>-0.001107511175879734</v>
       </c>
       <c r="U23" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -5577,13 +5577,13 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.552293411161106e-18</v>
+        <v>6.883107581431855e-17</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.473567287984773e-18</v>
+        <v>3.973964015000836e-17</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>35.97984078562226</v>
+        <v>35.97984078562279</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>-35.97984078562226</v>
+        <v>-35.97984078562279</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -5645,10 +5645,10 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.287962166476626e-13</v>
+        <v>-2.223293329050021e-13</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.219905416191566e-11</v>
+        <v>-5.558233322625052e-11</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.287962166476627e-13</v>
+        <v>2.223293329050021e-13</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>-1.287962166476627e-13</v>
+        <v>-2.223293329050021e-13</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5773,19 +5773,19 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.095376221225099e-14</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.023844055306275e-11</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="H25" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="I25" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -5797,13 +5797,13 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="N25" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="O25" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -5815,13 +5815,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="T25" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="U25" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5833,13 +5833,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5901,19 +5901,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1.214306433183765e-13</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="F26" t="n">
-        <v>3.035766082959412e-11</v>
+        <v>2.023844055306275e-11</v>
       </c>
       <c r="G26" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="I26" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -5925,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -5943,13 +5943,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="T26" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="U26" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5961,13 +5961,13 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-8.526512829121202e-14</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>8.526512829121202e-14</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6029,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-4.04768811061255e-11</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="H27" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="I27" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -6053,13 +6053,13 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="N27" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="O27" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -6071,13 +6071,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="T27" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="U27" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -6089,13 +6089,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="AA27" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="I28" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -6181,13 +6181,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -6199,13 +6199,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="U28" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -6217,13 +6217,13 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="Z28" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="AA28" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -6291,13 +6291,13 @@
         <v>-4.04768811061255e-11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="H29" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="I29" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -6309,13 +6309,13 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="N29" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="T29" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="U29" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6345,13 +6345,13 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="AA29" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6419,10 +6419,10 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -6437,10 +6437,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N30" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -6455,10 +6455,10 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="T30" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -6473,10 +6473,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -6541,10 +6541,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>-13.84864717531923</v>
+        <v>-13.84864717531928</v>
       </c>
       <c r="F31" t="n">
-        <v>-3462.161793829809</v>
+        <v>-3462.161793829819</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -6565,13 +6565,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="N31" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="O31" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -6601,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.004033370293736781</v>
+        <v>0.00403337029373678</v>
       </c>
       <c r="Z31" t="n">
-        <v>-0.0045363838309317</v>
+        <v>-0.004536383830931639</v>
       </c>
       <c r="AA31" t="n">
-        <v>-0.003546413586378977</v>
+        <v>-0.003546413586379021</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>13.84864717531926</v>
+        <v>13.84864717531929</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>-13.84864717531926</v>
+        <v>-13.84864717531929</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>13.84864717531942</v>
+        <v>13.84864717531945</v>
       </c>
       <c r="F32" t="n">
-        <v>3462.161793829856</v>
+        <v>3462.161793829863</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -6693,13 +6693,13 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="N32" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="O32" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -6711,13 +6711,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>6.8997973204105e-19</v>
+        <v>1.191049997705368e-18</v>
       </c>
       <c r="T32" t="n">
-        <v>-7.823634774238298e-19</v>
+        <v>-1.350523754131053e-18</v>
       </c>
       <c r="U32" t="n">
-        <v>9.033955285895597e-19</v>
+        <v>1.559450505989095e-18</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.0002967567251854169</v>
+        <v>0.000296756725185418</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.00180866020298177</v>
+        <v>0.001808660202981712</v>
       </c>
       <c r="AA32" t="n">
-        <v>-0.009215880681517411</v>
+        <v>-0.009215880681517451</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>-13.84864717531943</v>
+        <v>-13.84864717531946</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>13.84864717531943</v>
+        <v>13.84864717531946</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6797,10 +6797,10 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E33" t="n">
-        <v>15.48325824021185</v>
+        <v>15.48325824021166</v>
       </c>
       <c r="F33" t="n">
-        <v>3870.814560052963</v>
+        <v>3870.814560052914</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6821,13 +6821,13 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -6857,13 +6857,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.0003709459064817586</v>
+        <v>0.0003709459064817539</v>
       </c>
       <c r="Z33" t="n">
-        <v>-0.002069028233553117</v>
+        <v>-0.002069028233553033</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6875,7 +6875,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>-15.48325824021185</v>
+        <v>-15.48325824021166</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>15.48325824021185</v>
+        <v>15.48325824021166</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6925,13 +6925,13 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E34" t="n">
-        <v>-15.48325824021206</v>
+        <v>-15.48325824021186</v>
       </c>
       <c r="F34" t="n">
-        <v>-3870.814560053016</v>
+        <v>-3870.814560052966</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.3799594640821e-18</v>
+        <v>-2.382099995410737e-18</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="O34" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>6.171366335763509e-19</v>
+        <v>1.065307503788069e-18</v>
       </c>
       <c r="T34" t="n">
-        <v>-1.234273267152702e-18</v>
+        <v>-2.130615007576138e-18</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -6985,13 +6985,13 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>-0.000370945906481763</v>
+        <v>-0.0003709459064817577</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.002069028233553113</v>
+        <v>0.00206902823355303</v>
       </c>
       <c r="AA34" t="n">
-        <v>-0.00573048806595661</v>
+        <v>-0.005730488065956673</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -7003,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>15.48325824021206</v>
+        <v>15.48325824021186</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>-15.48325824021206</v>
+        <v>-15.48325824021186</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -7059,13 +7059,13 @@
         <v>-3462.161793829839</v>
       </c>
       <c r="G35" t="n">
-        <v>0.006910245705078549</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="H35" t="n">
-        <v>0.001418883819716404</v>
+        <v>0.001418883819716367</v>
       </c>
       <c r="I35" t="n">
-        <v>0.006207015870879429</v>
+        <v>0.006207015870879487</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -7077,13 +7077,13 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="N35" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="O35" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -7095,13 +7095,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.007207002430263966</v>
+        <v>0.00720700243026396</v>
       </c>
       <c r="T35" t="n">
-        <v>-0.006026821925871099</v>
+        <v>-0.006026821925871149</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0001682452488699993</v>
+        <v>0.0001682452488700487</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7113,13 +7113,13 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.006910245705078552</v>
+        <v>0.006910245705078545</v>
       </c>
       <c r="Z35" t="n">
-        <v>-0.006281299093253591</v>
+        <v>-0.006281299093253511</v>
       </c>
       <c r="AA35" t="n">
-        <v>-0.008038163939427563</v>
+        <v>-0.008038163939427604</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>13.84864717531934</v>
+        <v>13.8486471753194</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>-13.84864717531934</v>
+        <v>-13.8486471753194</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7181,19 +7181,19 @@
         <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>13.84864717531946</v>
+        <v>13.8486471753195</v>
       </c>
       <c r="F36" t="n">
-        <v>3462.161793829864</v>
+        <v>3462.161793829874</v>
       </c>
       <c r="G36" t="n">
-        <v>0.006910245705078548</v>
+        <v>0.006910245705078541</v>
       </c>
       <c r="H36" t="n">
-        <v>2.449185325764698e-05</v>
+        <v>2.449185325768649e-05</v>
       </c>
       <c r="I36" t="n">
-        <v>0.001292984129120605</v>
+        <v>0.001292984129120542</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -7205,13 +7205,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="N36" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="O36" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>-0.002876875411341767</v>
+        <v>-0.002876875411341762</v>
       </c>
       <c r="T36" t="n">
-        <v>0.003299098297921169</v>
+        <v>0.003299098297921221</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.005501221846268434</v>
+        <v>-0.005501221846268381</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7241,13 +7241,13 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>-0.00258011868615635</v>
+        <v>-0.002580118686156344</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.005735754367663588</v>
+        <v>0.005735754367663509</v>
       </c>
       <c r="AA36" t="n">
-        <v>-0.01181780866951986</v>
+        <v>-0.0118178086695199</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -7259,7 +7259,7 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>-13.84864717531946</v>
+        <v>-13.8486471753195</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -7277,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>13.84864717531946</v>
+        <v>13.8486471753195</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -7309,19 +7309,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E37" t="n">
-        <v>15.48325824021193</v>
+        <v>15.48325824021174</v>
       </c>
       <c r="F37" t="n">
-        <v>3870.814560052982</v>
+        <v>3870.814560052935</v>
       </c>
       <c r="G37" t="n">
-        <v>0.002016487163610129</v>
+        <v>0.002016487163610053</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0005935134503708136</v>
+        <v>0.0005935134503707814</v>
       </c>
       <c r="I37" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -7333,13 +7333,13 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -7351,13 +7351,13 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.001432655042953433</v>
+        <v>0.00143265504295337</v>
       </c>
       <c r="T37" t="n">
-        <v>-0.001538173665317278</v>
+        <v>-0.001538173665317224</v>
       </c>
       <c r="U37" t="n">
-        <v>0.00573048806595661</v>
+        <v>0.005730488065956673</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -7369,13 +7369,13 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.001803600949435193</v>
+        <v>0.001803600949435126</v>
       </c>
       <c r="Z37" t="n">
-        <v>-0.004934338319459988</v>
+        <v>-0.004934338319459721</v>
       </c>
       <c r="AA37" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>-15.48325824021192</v>
+        <v>-15.48325824021174</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -7405,7 +7405,7 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>15.48325824021192</v>
+        <v>15.48325824021174</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -7437,19 +7437,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E38" t="n">
-        <v>-15.48325824021211</v>
+        <v>-15.48325824021189</v>
       </c>
       <c r="F38" t="n">
-        <v>-3870.814560053027</v>
+        <v>-3870.814560052973</v>
       </c>
       <c r="G38" t="n">
-        <v>0.002016487163610131</v>
+        <v>0.002016487163610054</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.0005935134503708194</v>
+        <v>-0.0005935134503707861</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0009361786007100936</v>
+        <v>0.0009361786007100264</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -7461,13 +7461,13 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="O38" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -7479,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>-0.001432655042953438</v>
+        <v>-0.001432655042953374</v>
       </c>
       <c r="T38" t="n">
-        <v>0.001538173665317277</v>
+        <v>0.001538173665317223</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.0009361786007100936</v>
+        <v>-0.0009361786007100264</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>-0.001803600949435203</v>
+        <v>-0.001803600949435134</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.004934338319459983</v>
+        <v>0.004934338319459717</v>
       </c>
       <c r="AA38" t="n">
-        <v>-0.00426951193404345</v>
+        <v>-0.004269511934043515</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>15.4832582402121</v>
+        <v>15.48325824021189</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>-15.4832582402121</v>
+        <v>-15.48325824021189</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>6</v>
       </c>
       <c r="E39" t="n">
-        <v>-13.84864717531915</v>
+        <v>-13.84864717531936</v>
       </c>
       <c r="F39" t="n">
-        <v>-3462.161793829788</v>
+        <v>-3462.161793829839</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="H39" t="n">
-        <v>0.001858755894930333</v>
+        <v>0.001858755894930288</v>
       </c>
       <c r="I39" t="n">
-        <v>0.005000000000000029</v>
+        <v>0.005000000000000101</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -7589,13 +7589,13 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="N39" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -7607,13 +7607,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.00536825252855185</v>
+        <v>0.005368252528551776</v>
       </c>
       <c r="T39" t="n">
-        <v>-0.003276851444683104</v>
+        <v>-0.003276851444683088</v>
       </c>
       <c r="U39" t="n">
-        <v>0.01181780866951986</v>
+        <v>0.0118178086695199</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -7625,13 +7625,13 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.00507149580336644</v>
+        <v>0.005071495803366361</v>
       </c>
       <c r="Z39" t="n">
-        <v>-0.005713507514425525</v>
+        <v>-0.005713507514425355</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.004905638937448285</v>
+        <v>0.004905638937448047</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>13.84864717531914</v>
+        <v>13.84864717531937</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>-13.84864717531914</v>
+        <v>-13.84864717531937</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7693,19 +7693,19 @@
         <v>6</v>
       </c>
       <c r="E40" t="n">
-        <v>13.84864717531931</v>
+        <v>13.84864717531956</v>
       </c>
       <c r="F40" t="n">
-        <v>3462.161793829829</v>
+        <v>3462.16179382989</v>
       </c>
       <c r="G40" t="n">
-        <v>0.01227849823363042</v>
+        <v>0.0122784982336304</v>
       </c>
       <c r="H40" t="n">
-        <v>0.001027995451017786</v>
+        <v>0.001027995451017834</v>
       </c>
       <c r="I40" t="n">
-        <v>6.98034996549076e-18</v>
+        <v>-6.752144827409786e-17</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -7717,13 +7717,13 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="N40" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="O40" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.005368252528551873</v>
+        <v>-0.005368252528551795</v>
       </c>
       <c r="T40" t="n">
-        <v>0.007641209249402963</v>
+        <v>0.007641209249402946</v>
       </c>
       <c r="U40" t="n">
-        <v>0.008038163939427563</v>
+        <v>0.008038163939427604</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -7753,13 +7753,13 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.005071495803366459</v>
+        <v>-0.005071495803366376</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.007895686416785464</v>
+        <v>0.007895686416785296</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.003015816572402124</v>
+        <v>0.003015816572401887</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>-13.84864717531931</v>
+        <v>-13.84864717531957</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>13.84864717531931</v>
+        <v>13.84864717531957</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7821,19 +7821,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E41" t="n">
-        <v>15.48325824021209</v>
+        <v>15.48325824021191</v>
       </c>
       <c r="F41" t="n">
-        <v>3870.814560053023</v>
+        <v>3870.814560052978</v>
       </c>
       <c r="G41" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0005935134503708089</v>
+        <v>0.000593513450370752</v>
       </c>
       <c r="I41" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -7845,10 +7845,10 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N41" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.002865310085906864</v>
+        <v>0.002865310085906693</v>
       </c>
       <c r="T41" t="n">
-        <v>-0.004403483751224152</v>
+        <v>-0.004403483751223937</v>
       </c>
       <c r="U41" t="n">
-        <v>0.00426951193404345</v>
+        <v>0.004269511934043515</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -7881,10 +7881,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.003236255992388629</v>
+        <v>0.003236255992388453</v>
       </c>
       <c r="Z41" t="n">
-        <v>-0.00647251198477725</v>
+        <v>-0.006472511984776729</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-15.48325824021209</v>
+        <v>-15.48325824021192</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>15.48325824021209</v>
+        <v>15.48325824021192</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>6.708203932499369</v>
       </c>
       <c r="E42" t="n">
-        <v>-15.48325824021231</v>
+        <v>-15.48325824021211</v>
       </c>
       <c r="F42" t="n">
-        <v>-3870.814560053077</v>
+        <v>-3870.814560053027</v>
       </c>
       <c r="G42" t="n">
-        <v>0.005220001227961893</v>
+        <v>0.005220001227961625</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.00059351345037082</v>
+        <v>-0.0005935134503707612</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0009361786007100781</v>
+        <v>-0.0009361786007101457</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -7973,10 +7973,10 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N42" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -7991,13 +7991,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.002865310085906874</v>
+        <v>-0.002865310085906701</v>
       </c>
       <c r="T42" t="n">
-        <v>0.004403483751224147</v>
+        <v>0.004403483751223933</v>
       </c>
       <c r="U42" t="n">
-        <v>0.0009361786007100781</v>
+        <v>0.0009361786007101457</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>-0.003236255992388644</v>
+        <v>-0.003236255992388466</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.006472511984777243</v>
+        <v>0.006472511984776723</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -8027,7 +8027,7 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>15.48325824021231</v>
+        <v>15.48325824021211</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>-15.48325824021231</v>
+        <v>-15.48325824021211</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -8077,19 +8077,19 @@
         <v>6</v>
       </c>
       <c r="E43" t="n">
-        <v>-13.84864717531917</v>
+        <v>-13.84864717531942</v>
       </c>
       <c r="F43" t="n">
-        <v>-3462.161793829794</v>
+        <v>-3462.161793829854</v>
       </c>
       <c r="G43" t="n">
-        <v>0.008986496724337876</v>
+        <v>0.008986496724337585</v>
       </c>
       <c r="H43" t="n">
-        <v>0.001418883819716412</v>
+        <v>0.001418883819716362</v>
       </c>
       <c r="I43" t="n">
-        <v>0.003792984129120626</v>
+        <v>0.003792984129120687</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -8101,10 +8101,10 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N43" t="n">
-        <v>2.947134575969546e-18</v>
+        <v>7.947928030001671e-17</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -8119,13 +8119,13 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.003915000920971418</v>
+        <v>0.003915000920971208</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.002294043079055072</v>
+        <v>-0.00229404307905491</v>
       </c>
       <c r="U43" t="n">
-        <v>0.008750269562383884</v>
+        <v>0.008750269562383738</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -8137,13 +8137,13 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.003618244195786007</v>
+        <v>0.003618244195785792</v>
       </c>
       <c r="Z43" t="n">
-        <v>-0.004102703282036856</v>
+        <v>-0.004102703282036496</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.004737393688578282</v>
+        <v>0.004737393688577926</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>13.84864717531917</v>
+        <v>13.84864717531943</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-13.84864717531917</v>
+        <v>-13.84864717531943</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8205,19 +8205,19 @@
         <v>6</v>
       </c>
       <c r="E44" t="n">
-        <v>13.84864717531934</v>
+        <v>13.84864717531956</v>
       </c>
       <c r="F44" t="n">
-        <v>3462.161793829834</v>
+        <v>3462.16179382989</v>
       </c>
       <c r="G44" t="n">
-        <v>0.008986496724337874</v>
+        <v>0.008986496724337583</v>
       </c>
       <c r="H44" t="n">
-        <v>2.449185325764975e-05</v>
+        <v>2.44918532577016e-05</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.001292984129120591</v>
+        <v>-0.001292984129120654</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8229,10 +8229,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.00723648839157201</v>
+        <v>0.007236488391571465</v>
       </c>
       <c r="N44" t="n">
-        <v>-2.002412356229263e-17</v>
+        <v>-9.340821653536937e-17</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -8247,13 +8247,13 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.003915000920971435</v>
+        <v>-0.003915000920971222</v>
       </c>
       <c r="T44" t="n">
-        <v>0.00447622198141501</v>
+        <v>0.004476221981414849</v>
       </c>
       <c r="U44" t="n">
-        <v>0.00686044719733772</v>
+        <v>0.006860447197337577</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -8265,13 +8265,13 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>-0.00361824419578602</v>
+        <v>-0.003618244195785803</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.004102703282036844</v>
+        <v>0.004102703282036487</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.004737393688578282</v>
+        <v>0.004737393688577926</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-13.84864717531934</v>
+        <v>-13.84864717531957</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>13.84864717531934</v>
+        <v>13.84864717531957</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>

--- a/outputs/validation_truss_supp_disp.xlsx
+++ b/outputs/validation_truss_supp_disp.xlsx
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>35.97984078562254</v>
+        <v>35.97984078562255</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-35.97984078562254</v>
+        <v>-35.97984078562255</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -3163,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>11.99328026187402</v>
+        <v>11.99328026187399</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-11.99328026187402</v>
+        <v>-11.99328026187399</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -3419,7 +3419,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>4.04768811061255e-14</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-4.04768811061255e-14</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -3547,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.371347480016993e-12</v>
+        <v>1.371154347470001e-12</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>-1.371347480016993e-12</v>
+        <v>-1.371154347470001e-12</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>1.011922027653137e-13</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>-1.011922027653137e-13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -3949,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>27.69729435063946</v>
+        <v>27.69729435063945</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -4077,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>-27.69729435063946</v>
+        <v>-27.69729435063945</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -4187,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-35.97984078562309</v>
+        <v>-35.97984078562308</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>35.97984078562309</v>
+        <v>35.97984078562308</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>27.69729435063669</v>
+        <v>27.69729435063668</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -4333,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>-27.69729435063669</v>
+        <v>-27.69729435063668</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-6.071532165918825e-14</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>6.071532165918825e-14</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-11.9932802618743</v>
+        <v>-11.99328026187431</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>11.9932802618743</v>
+        <v>11.99328026187431</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -4827,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>5.059610138265687e-15</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>-5.059610138265687e-15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -4955,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-1.158184659288963e-12</v>
+        <v>-1.158650721662842e-12</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.158184659288963e-12</v>
+        <v>1.158650721662842e-12</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>5.565571152092256e-14</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-5.565571152092256e-14</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>-27.69729435063924</v>
+        <v>-27.69729435063923</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -5485,7 +5485,7 @@
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>27.69729435063924</v>
+        <v>27.69729435063923</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -5979,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>-8.526512829121202e-14</v>
+        <v>-8.095376221225099e-14</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>8.526512829121202e-14</v>
+        <v>8.095376221225099e-14</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>1.61907524424502e-13</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>-1.61907524424502e-13</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>13.84864717531929</v>
+        <v>13.84864717531928</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>-13.84864717531929</v>
+        <v>-13.84864717531928</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>-13.84864717531946</v>
+        <v>-13.84864717531945</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -6765,7 +6765,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>13.84864717531946</v>
+        <v>13.84864717531945</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>13.8486471753194</v>
+        <v>13.84864717531936</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -7149,7 +7149,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>-13.8486471753194</v>
+        <v>-13.84864717531936</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -7643,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>13.84864717531937</v>
+        <v>13.84864717531936</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>-13.84864717531937</v>
+        <v>-13.84864717531936</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7771,7 +7771,7 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>-13.84864717531957</v>
+        <v>-13.84864717531956</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>13.84864717531957</v>
+        <v>13.84864717531956</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>-15.48325824021192</v>
+        <v>-15.48325824021191</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>15.48325824021192</v>
+        <v>15.48325824021191</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>13.84864717531943</v>
+        <v>13.84864717531942</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>-13.84864717531943</v>
+        <v>-13.84864717531942</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>-13.84864717531957</v>
+        <v>-13.84864717531956</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -8301,7 +8301,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>13.84864717531957</v>
+        <v>13.84864717531956</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
